--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer with Databricks and GCP</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer with Databricks and GCP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
         </is>
       </c>
     </row>
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
+          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARTDAI</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
+          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ARTDAI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Researcher II - Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>National Renewable Energy Laboratory</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d00084c72cc397</t>
+          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, API Gateway, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>API Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=81aef2a88bea4b42</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Diverse Lynx</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Diverse Lynx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,147 +2411,147 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Data Architect and Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Numerica Credit Union</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Celero Commerce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c8daa35e715d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a748882073b3e83f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f73817f5130d34</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95be70644e7fea</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a748882073b3e83f</t>
+          <t>https://www.indeed.com/viewjob?jk=871870387466171e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f73817f5130d34</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95be70644e7fea</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871870387466171e</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,19 +3366,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=cc956ee1692fe630</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Polars, MySQL, NoSQL, Maven, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=3aadd87cb24ca793</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Polars, MySQL, NoSQL, Maven, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aadd87cb24ca793</t>
+          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Systems and SaaS Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Minted</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,29 +3986,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Spark, Scala, Splunk, Terraform, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=58558f0623f5281d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Systems and SaaS Engineer</t>
+          <t>AI/Data Scientist II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Minted</t>
+          <t>Premera Blue Cross</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Spark, Scala, Splunk, Terraform, Git</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, SQL Server, NoSQL, Data Modeling, Tableau, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58558f0623f5281d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea032120825aad4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Developer II - Data Science &amp; Enterprise Data Platform Development</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Scala, Kafka, Snowflake, ELT, Airflow, Apache Airflow, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cd0f856172e7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,24 +4161,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Vertex AI, CI/CD, Jenkins, GitHub Actions, Maven, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Engineer, Cloud</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
         </is>
       </c>
     </row>
@@ -4563,17 +4563,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,24 +4686,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Enterprise Architect - Data</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Data</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c801e823db82192</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5ca1e5454ee8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,157 +5036,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>LG Ad Solutions</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Business Analytics Product Owner</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Texas Capital Bank</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (PHP)</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Vacatia, Inc.</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Changeis, Inc.</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=accb0ee41fababc7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
@@ -1553,52 +1553,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,24 +1676,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>API Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81aef2a88bea4b42</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>API Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
+          <t>https://www.indeed.com/viewjob?jk=81aef2a88bea4b42</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Architect: Risk, Marketing and Admin Systems</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Diverse Lynx</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Diverse Lynx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
@@ -2206,29 +2206,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect and Data Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Numerica Credit Union</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect and Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Numerica Credit Union</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a748882073b3e83f</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f73817f5130d34</t>
+          <t>https://www.indeed.com/viewjob?jk=a748882073b3e83f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95be70644e7fea</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f73817f5130d34</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871870387466171e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95be70644e7fea</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=871870387466171e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,19 +3366,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc956ee1692fe630</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc956ee1692fe630</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Analytics/Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Radost Solutions LLC</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Analytics/Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radost Solutions LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Systems and SaaS Engineer</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Minted</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Spark, Scala, Splunk, Terraform, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,19 +3996,19 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58558f0623f5281d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI/Data Scientist II</t>
+          <t>Systems and SaaS Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Premera Blue Cross</t>
+          <t>Minted</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, SQL Server, NoSQL, Data Modeling, Tableau, Python</t>
+          <t>AWS, S3, IAM, RDS, Azure, Spark, Scala, Splunk, Terraform, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea032120825aad4</t>
+          <t>https://www.indeed.com/viewjob?jk=58558f0623f5281d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>AI/Data Scientist II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Premera Blue Cross</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, SQL Server, NoSQL, Data Modeling, Tableau, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea032120825aad4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Engineer, Cloud</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,24 +4686,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Data</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Architect - Data</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
@@ -4983,17 +4983,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,15 +5036,50 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PHP)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Vacatia, Inc.</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -2206,29 +2206,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1599edcc63d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Data Architect and Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Numerica Credit Union</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect and Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Numerica Credit Union</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=a748882073b3e83f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a748882073b3e83f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f73817f5130d34</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f73817f5130d34</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95be70644e7fea</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95be70644e7fea</t>
+          <t>https://www.indeed.com/viewjob?jk=871870387466171e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871870387466171e</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,19 +3366,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Architect: Risk, Marketing and Admin Systems</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Diverse Lynx</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2abed7066b82ae</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect and Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Numerica Credit Union</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Test Automation Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=890d646a91ef01b8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Polars, MySQL, NoSQL, Maven, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aadd87cb24ca793</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Engineer - III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Vanguard</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc956ee1692fe630</t>
+          <t>https://www.indeed.com/viewjob?jk=781024c719b3e436</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer Microservices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3527869070a089</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Sr. Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Polars, MySQL, NoSQL, Maven, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=3aadd87cb24ca793</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=cc956ee1692fe630</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Analytics/Data Engineer</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Radost Solutions LLC</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,59 +3856,59 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Senior Analytics/Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Radost Solutions LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Systems and SaaS Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Minted</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Spark, Scala, Splunk, Terraform, Git</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58558f0623f5281d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI/Data Scientist II</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Premera Blue Cross</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, SQL Server, NoSQL, Data Modeling, Tableau, Python</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea032120825aad4</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Systems and SaaS Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Minted</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Spark, Scala, Splunk, Terraform, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=58558f0623f5281d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>AI/Data Scientist II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Premera Blue Cross</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, SQL Server, NoSQL, Data Modeling, Tableau, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea032120825aad4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,59 +4486,59 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Cloud</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Data</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,29 +4826,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Enterprise Architect - Data</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,15 +5071,120 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Kingston, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Business Analytics Product Owner</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Texas Capital Bank</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PHP)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Vacatia, Inc.</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Architect, Data</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8f5d1958986efa</t>
+          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0eb1930f6c3830</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8f5d1958986efa</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6b4c094d34de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0eb1930f6c3830</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae79c8e8bf869344</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6b4c094d34de4c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>Architect, Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
+          <t>https://www.indeed.com/viewjob?jk=ae79c8e8bf869344</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>API Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=81aef2a88bea4b42</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>API Developer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81aef2a88bea4b42</t>
+          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Architect: Risk, Marketing and Admin Systems</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f467cbd6c1fe6e</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,77 +2341,77 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, Spark, Kafka, Dask, MongoDB, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=b8f95c86a9a4e627</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=18938060c32c52cd</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
@@ -3198,25 +3198,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=377676b1c3880e52</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,19 +3366,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Test Automation Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890d646a91ef01b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Test Automation Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>DS Technologies Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=890d646a91ef01b8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Engineer - III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vanguard</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781024c719b3e436</t>
+          <t>https://www.indeed.com/viewjob?jk=cc956ee1692fe630</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer Microservices</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3527869070a089</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer</t>
+          <t>Application Engineer - III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Vanguard</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Polars, MySQL, NoSQL, Maven, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aadd87cb24ca793</t>
+          <t>https://www.indeed.com/viewjob?jk=781024c719b3e436</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer Microservices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc956ee1692fe630</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3527869070a089</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Sr. Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Polars, MySQL, NoSQL, Maven, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=3aadd87cb24ca793</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,69 +3881,69 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Analytics/Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Radost Solutions LLC</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Analytics/Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radost Solutions LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Systems and SaaS Engineer</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Minted</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Spark, Scala, Splunk, Terraform, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,19 +4136,19 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58558f0623f5281d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI/Data Scientist II</t>
+          <t>Systems and SaaS Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Premera Blue Cross</t>
+          <t>Minted</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, SQL Server, NoSQL, Data Modeling, Tableau, Python</t>
+          <t>AWS, S3, IAM, RDS, Azure, Spark, Scala, Splunk, Terraform, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea032120825aad4</t>
+          <t>https://www.indeed.com/viewjob?jk=58558f0623f5281d</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
@@ -5018,17 +5018,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Senior Consultant - Data Engineering &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Black &amp; Veatch</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c1aa86a59e2c6c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=f9eb22e24231f22b</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=469d8b6a01022163</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,15 +5176,225 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eced1a3a797949e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07382ba85bed2a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9813268f71a7390</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Kingston, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>LG Ad Solutions</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Business Analytics Product Owner</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Texas Capital Bank</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PHP)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Vacatia, Inc.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Architect, Data</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8f5d1958986efa</t>
+          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Architect, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0eb1930f6c3830</t>
+          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Architect, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6b4c094d34de4c</t>
+          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Architect, Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>ARTDAI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae79c8e8bf869344</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
+          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Researcher II - Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARTDAI</t>
+          <t>National Renewable Energy Laboratory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
+          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Researcher II - Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>National Renewable Energy Laboratory</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>National Alliance on Mental Illness</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,164 +1441,164 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>API Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=81aef2a88bea4b42</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>API Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81aef2a88bea4b42</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Architect: Risk, Marketing and Admin Systems</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, MongoDB, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8f95c86a9a4e627</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18938060c32c52cd</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a748882073b3e83f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f73817f5130d34</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95be70644e7fea</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871870387466171e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AWS Engineer - Remote - Contract</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cherokee Federal</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377676b1c3880e52</t>
+          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Analytics/Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radost Solutions LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,137 +3506,137 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Test Automation Architect</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DS Technologies Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890d646a91ef01b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc956ee1692fe630</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Application Engineer - III</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vanguard</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=781024c719b3e436</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer Microservices</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3527869070a089</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Polars, MySQL, NoSQL, Maven, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aadd87cb24ca793</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,59 +3891,59 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Analytics/Data Engineer</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Radost Solutions LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed775e5478fbbc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>Senior Engineer, Cloud</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Systems and SaaS Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Minted</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Spark, Scala, Splunk, Terraform, Git</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58558f0623f5281d</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>SRE Engineer with Spanish/Portuguese</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,137 +4276,137 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud</t>
+          <t>Enterprise Architect - Data</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,742 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Specialist - Architecture</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Bloomington, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Lumistry</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>NELSON Worldwide</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Andersen</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>GCP Data Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Enterprise Architect - Data</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Integral Ad Science</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Integral Ad Science</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Consultant - Data Engineering &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Black &amp; Veatch</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c1aa86a59e2c6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Sr. Spclst , Software Engineering</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Merck</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>North Wales, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9eb22e24231f22b</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=469d8b6a01022163</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eced1a3a797949e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07382ba85bed2a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>ERP &amp; Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Missouri State University</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9813268f71a7390</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Kingston, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>LG Ad Solutions</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Business Analytics Product Owner</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Texas Capital Bank</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (PHP)</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Vacatia, Inc.</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,42 +573,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - Databricks &amp; GCP</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafb0baf34406e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
+          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
+          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
+          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>ARTDAI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARTDAI</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
+          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>Researcher II - Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>National Renewable Energy Laboratory</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Researcher II - Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>National Renewable Energy Laboratory</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>National Alliance on Mental Illness</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, Databricks, Blob Storage, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed711fef7ac0518</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Nobl Q</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>API Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81aef2a88bea4b42</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Architect: Risk, Marketing and Admin Systems</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,137 +2281,137 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,24 +2551,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Engineer - Remote - Contract</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Engineer - Remote - Contract</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics/Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Radost Solutions LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Analytics/Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Radost Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Senior Engineer, Cloud</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SRE Engineer with Spanish/Portuguese</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,24 +4266,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, AKS, Datadog</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd93501e0d644195</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,29 +4301,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Enterprise Architect - Data</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4590,76 +4590,6 @@
         </is>
       </c>
       <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (PHP)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Vacatia, Inc.</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Enterprise Architect - Data</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud AI Consultant</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f88eed34169f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer with Databricks and GCP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,24 +521,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer with Databricks and GCP</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -561,12 +561,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+          <t>https://www.indeed.com/viewjob?jk=1215d222f0829a74</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1741abb6e46be8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
         </is>
       </c>
     </row>
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
+          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>ARTDAI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARTDAI</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
+          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>Researcher II - Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>National Renewable Energy Laboratory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Researcher II - Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>National Renewable Energy Laboratory</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,42 +1336,42 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Cloud Platform Architect 6184507</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9c6db3ce25d4ca</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
+          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,24 +2586,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OCI Terraform Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Engineer - Remote - Contract</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>AWS Engineer - Remote - Contract</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Analytics/Data Engineer</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Radost Solutions LLC</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Analytics/Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radost Solutions LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior AWS FinOps Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=68fa6a156ca0e34f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3e5ad47ba3b415</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01924ffd1d906ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Engineer, Cloud</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07ad7e085e29db9</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,17 +4546,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer with Databricks and GCP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer with Databricks and GCP</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nobl Q</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Hadoop, Spark, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b30760f90abab6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,29 +1471,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Cloud Platform Architect 6184507</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,77 +1536,77 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9c6db3ce25d4ca</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9c6db3ce25d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,77 +1991,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,104 +2236,104 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,24 +3146,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,59 +3436,59 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Analytics/Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Radost Solutions LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785566154ce81c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Analytics/Data Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Radost Solutions LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,24 +3566,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior AWS FinOps Specialist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=68fa6a156ca0e34f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,24 +3636,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AWS FinOps Specialist</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fa6a156ca0e34f</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,24 +4196,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,29 +4231,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Enterprise Architect - Data</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,50 +4546,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Enterprise Architect - Data</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer with Databricks and GCP</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer with Databricks and GCP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea17e136a8a1893e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud Platform Architect 6184507</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9c6db3ce25d4ca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9c6db3ce25d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,24 +3111,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>AWS Engineer - Remote - Contract</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Engineer - Remote - Contract</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Database Management Specialist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>3Bstaffing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,59 +3401,59 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Analytics/Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Radost Solutions LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Analytics/Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Radost Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Senior AWS FinOps Specialist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,24 +3566,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=68fa6a156ca0e34f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AWS FinOps Specialist</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3601,24 +3601,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fa6a156ca0e34f</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,24 +4126,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer with Databricks and GCP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer with Databricks and GCP</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2a775f522cf48c</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212b9ffd779d7d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,52 +2166,52 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e1d27693a96f5</t>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,24 +3076,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>AWS Engineer - Remote - Contract</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Engineer - Remote - Contract</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Database Management Specialist</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3Bstaffing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea99aacea583d180</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Analytics/Data Engineer</t>
+          <t>Senior AWS FinOps Specialist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Radost Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,24 +3461,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51b41b3f39ad8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=68fa6a156ca0e34f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AWS FinOps Specialist</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,24 +3566,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fa6a156ca0e34f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,102 +3751,102 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,24 +4091,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,29 +4126,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Enterprise Architect - Data</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,85 +4476,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Java Developer (AWS)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Enterprise Architect - Data</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer with Databricks and GCP</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,104 +486,104 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1215d222f0829a74</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1215d222f0829a74</t>
+          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,49 +601,49 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>UKG Workforce Analytics Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,37 +666,37 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
+          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
+          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>ARTDAI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARTDAI</t>
+          <t>Green Gas USA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Platform Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,42 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
@@ -1413,105 +1413,105 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9c6db3ce25d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,24 +1781,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>OCI MySQL HeatWave Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,102 +1826,102 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,139 +2061,139 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>EV Design</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>OCI API Gateway Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Engineer - Remote - Contract</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,94 +3146,94 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3247,11 +3247,11 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>OCI AI Services Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1c10adddc53fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AWS FinOps Specialist</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fa6a156ca0e34f</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,102 +3611,102 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Lumistry</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>NELSON Worldwide</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Airflow, Git</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+          <t>Enterprise Architect - Data</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,365 +4126,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, Snowflake, Informatica PowerCenter, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Integral Ad Science</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Integral Ad Science</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Sr. Spclst , Software Engineering</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Merck</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>North Wales, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>LG Ad Solutions</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Backend)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Kingston, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Business Analytics Product Owner</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Texas Capital Bank</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (PHP)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Vacatia, Inc.</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Java Developer (AWS)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Enterprise Architect - Data</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,77 +468,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce1ac0502e490cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1215d222f0829a74</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1215d222f0829a74</t>
+          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,46 +552,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869e1075742399ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
+          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ARTDAI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
+          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UKG Workforce Analytics Consultant</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Green Gas USA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc50b92edc01612c</t>
+          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
+          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Telematics Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ARTDAI</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
+          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Green Gas USA</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Researcher II - Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>National Renewable Energy Laboratory</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
+          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior .Net Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=a27509362b1441a6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>Senior .Net Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=f3769548913d0b45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Researcher II - Data Scientist</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>National Renewable Energy Laboratory</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AllianceBernstein</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer (Remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OCI Storage Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1462,33 +1462,33 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,46 +1497,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mohawk Industries</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3b58d4d246597</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,277 +1721,277 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OCI MySQL HeatWave Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, NoSQL, MS Excel, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e7be674cd49261</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,129 +2631,129 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EV Design</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7b188a1549b300</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OCI API Gateway Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4d365388991b60</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,452 +3191,452 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, IAM, RDS, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI-Driven OSINT Analyst</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OCI AI Services Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05d70602a2cc6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,277 +3681,277 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NELSON Worldwide</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c00f169f86ba3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,137 +3961,137 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,40 +4101,1755 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior ML Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Prudential</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Application Platform Architect - 6163848</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Logic, Inc.</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sr Database Engineer (DBE)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BECU</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data Analytics &amp; Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Authority Brands</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FULL-STACK DEVELOPER</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Quartech</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Store Efficiency</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Foot Locker</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Medefy Health</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>IT Data Solutions Developer Senior</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HARBIN CLINIC</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RapidFire Safety &amp; Security</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Reporting &amp; Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ABOUT Healthcare</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Digital Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PDI</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Woodcliff Lake, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Revelyst</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Specialist - Architecture</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Bloomington, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Data Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>LG Ad Solutions</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Lumistry</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Integral Ad Science</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Integral Ad Science</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sr. Spclst , Software Engineering</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Merck</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>North Wales, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>LG Ad Solutions</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Backend)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Kingston, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Business Analytics Product Owner</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Texas Capital Bank</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PHP)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Vacatia, Inc.</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (AWS)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>Enterprise Architect - Data</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>Englewood, CO, US USA</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D155" t="n">
         <v>10.4</v>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IAM DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d38624bd76610a</t>
+          <t>https://www.indeed.com/viewjob?jk=882db95cb994b7c6</t>
         </is>
       </c>
     </row>
@@ -1483,52 +1483,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer-(SAS-to-Snowflake Migration)-USC/GC***</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a545b8dcc319311</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mohawk Industries</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1ff454e07b8ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,139 +1641,139 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>Senior Engineer, Infrastructure (DevOps)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Pryon</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Senior Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,77 +2376,77 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>FULL-STACK DEVELOPER</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Quartech</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,104 +4966,104 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Security Compliance Specialist</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=f276a316b4b1e560</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
@@ -5508,17 +5508,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Compliance Automation Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Dataflow, Scala, Data Modeling, Dimensional Modeling, Power BI, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d99ca2e5dd772a4</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Data</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,17 +5841,87 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Enterprise Architect - Data</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>IAM DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff2f3126ab0313df</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,35 +608,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Qlik Data Engineer-6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARTDAI</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d6c6fc6970faee1</t>
+          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IAM DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882db95cb994b7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>IAM DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=882db95cb994b7c6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1462,46 +1462,46 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Data Engineer with AI/ML</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,129 +1756,129 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JavaFull Stack / DevOps / Cloud Deployment</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1cf1102bd9b8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Test Automation Engineer with Payments-6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e317823b6bba5c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Developer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Cloud Storage, Spark, Scala, Data Modeling, Kimball</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c4e157289a567</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FULL-STACK DEVELOPER</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Quartech</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB, ETL, Power BI, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c717e9173db492f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
@@ -5018,17 +5018,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Security Compliance Specialist</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f276a316b4b1e560</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Security Compliance Specialist</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=f276a316b4b1e560</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Medefy Health</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,77 +5281,77 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Lumistry</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606dcec420e3ba3d</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Compliance Automation Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Data Modeling, Dimensional Modeling, Power BI, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Software Engineer II, Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake Architect-6</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>Minnesota City, MN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e9660980ec8a8c</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Azure Databricks Architect-6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=45a02b9b0db8bbb2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Adobe Cloud Architect-6</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=57de77eeafd2c392</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Snowflake Architect-6</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=6186e5dd2c86d2eb</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Data</t>
+          <t>Senior Compliance Automation Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>RDS, Dataflow, Scala, Data Modeling, Dimensional Modeling, Power BI, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>IAM DevSecOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,15 +5911,400 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Integral Ad Science</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Sr. Spclst , Software Engineering</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Merck</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>North Wales, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>LG Ad Solutions</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Business Analytics Product Owner</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Texas Capital Bank</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Backend)</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Kingston, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Data Analyst_EDM-7</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Teradata Developer-6</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (AWS)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Enterprise Architect - Data</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>IAM DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
           <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff2f3126ab0313df</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Qlik Data Engineer-6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
+          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-6</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Green Gas USA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Green Gas USA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
+          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Researcher II - Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>National Renewable Energy Laboratory</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,137 +706,137 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
+          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Telematics Data Engineer</t>
+          <t>Senior .Net Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3602426cadbf5f73</t>
+          <t>https://www.indeed.com/viewjob?jk=a27509362b1441a6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior .Net Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3769548913d0b45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Researcher II - Data Scientist</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>National Renewable Energy Laboratory</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior .Net Developer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27509362b1441a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior .Net Developer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3769548913d0b45</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IAM DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=882db95cb994b7c6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IAM DevSecOps Engineer</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882db95cb994b7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,89 +1301,89 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,291 +1392,291 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Architect: Risk, Marketing and Admin Systems</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Service Consultant, Automation Enablement Security Engineer Expert</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, NoSQL, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=ff94dfe3f61f8ecd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,172 +1826,172 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer, Design Innovation</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=93163132c02c54e2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,94 +2106,94 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Test Automation Engineer with Payments-6</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e317823b6bba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Test Automation Engineer with Payments-6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e317823b6bba5c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,42 +4966,42 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Security Compliance Specialist</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f276a316b4b1e560</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,94 +5151,94 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Medefy Health</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b017509b0a14a7</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineering Intern - DRC Team</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>StockX</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b144a0f72c9e40</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Security Compliance Specialist</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,42 +5386,42 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=f276a316b4b1e560</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,67 +5466,67 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,67 +5536,67 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, Airflow</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,94 +5606,94 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f0a13fefa0a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Snowflake Architect-6</t>
+          <t>Senior Full Stack Developer in Merrimack, NH</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Minnesota City, MN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e9660980ec8a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-6</t>
+          <t>Reporting &amp; Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ABOUT Healthcare</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45a02b9b0db8bbb2</t>
+          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Adobe Cloud Architect-6</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57de77eeafd2c392</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Snowflake Architect-6</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6186e5dd2c86d2eb</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Compliance Automation Engineer</t>
+          <t>Snowflake Architect-6</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnesota City, MN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Data Modeling, Dimensional Modeling, Power BI, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e9660980ec8a8c</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Azure Databricks Architect-6</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=45a02b9b0db8bbb2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Adobe Cloud Architect-6</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=57de77eeafd2c392</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Snowflake Architect-6</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=6186e5dd2c86d2eb</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, NoSQL, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>Senior Technical Data Analyst</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>GHX</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,29 +6051,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, Redshift, ECS, RDS, Scala, Polars, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=6b94c4bc25bde3f7</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>Senior Compliance Automation Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>RDS, Dataflow, Scala, Data Modeling, Dimensional Modeling, Power BI, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Data</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>IAM DevSecOps Engineer</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,15 +6296,260 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Backend)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Kingston, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Data Analyst_EDM-7</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Teradata Developer-6</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (AWS)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Enterprise Architect - Data</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>IAM DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
           <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff2f3126ab0313df</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Researcher II - Data Scientist</t>
+          <t>Senior .Net Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>National Renewable Energy Laboratory</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Azure, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040a0e21b7819ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=a27509362b1441a6</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27509362b1441a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f3769548913d0b45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior .Net Developer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3769548913d0b45</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IAM DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=882db95cb994b7c6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IAM DevSecOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,52 +1046,52 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882db95cb994b7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Service Consultant, Automation Enablement Security Engineer Expert</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, NoSQL, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff94dfe3f61f8ecd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Service Consultant, Automation Enablement Security Engineer Expert</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, NoSQL, ELT, Splunk, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff94dfe3f61f8ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
         </is>
       </c>
     </row>
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,42 +1861,42 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Architect: Risk, Marketing and Admin Systems</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfd53eefe4f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
@@ -5158,17 +5158,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Data Analytics &amp; Power BI Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,52 +5176,52 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
@@ -5648,35 +5648,35 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Reporting &amp; Business Intelligence Developer</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ABOUT Healthcare</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82bc310c78840492</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
@@ -5718,17 +5718,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Snowflake Architect-6</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Minnesota City, MN, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,24 +5876,24 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e9660980ec8a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-6</t>
+          <t>Snowflake Architect-6</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Minnesota City, MN, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,14 +5921,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45a02b9b0db8bbb2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e9660980ec8a8c</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Adobe Cloud Architect-6</t>
+          <t>Azure Databricks Architect-6</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,14 +5956,14 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57de77eeafd2c392</t>
+          <t>https://www.indeed.com/viewjob?jk=45a02b9b0db8bbb2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Snowflake Architect-6</t>
+          <t>Adobe Cloud Architect-6</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6186e5dd2c86d2eb</t>
+          <t>https://www.indeed.com/viewjob?jk=57de77eeafd2c392</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Snowflake Architect-6</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=6186e5dd2c86d2eb</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Technical Data Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GHX</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Scala, Polars, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b94c4bc25bde3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>Senior Technical Data Analyst</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GHX</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, Redshift, ECS, RDS, Scala, Polars, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b94c4bc25bde3f7</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Compliance Automation Engineer</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Data Modeling, Dimensional Modeling, Power BI, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Compliance Automation Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,17 +6226,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Dataflow, Scala, Data Modeling, Dimensional Modeling, Power BI, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Data Analyst_EDM-7</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Mid-Hudson Valley Federal Credit Union</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Kingston, NY, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
+          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Teradata Developer-6</t>
+          <t>Business Analytics Product Owner</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
+          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Java Developer (AWS)</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Enterprise Architect - Data</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>IAM DevSecOps Engineer</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,15 +6541,85 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Enterprise Architect - Data</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>IAM DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
           <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff2f3126ab0313df</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-6</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Green Gas USA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Green Gas USA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
+          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Sr. Qlik Data Engineer-6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
+          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior .Net Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27509362b1441a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3769548913d0b45</t>
+          <t>https://www.indeed.com/viewjob?jk=a27509362b1441a6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Senior .Net Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f3769548913d0b45</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IAM DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882db95cb994b7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>IAM DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,69 +1046,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=882db95cb994b7c6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf01d968e498d3c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Development Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0615dac006ebd6dd</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
+          <t>https://www.indeed.com/viewjob?jk=e890f897231a1e5f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=edecc428ad4e52e1</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
+          <t>https://www.indeed.com/viewjob?jk=a28480a9e54addee</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2f2413f04206c9d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
+          <t>https://www.indeed.com/viewjob?jk=1453b4d57f424698</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
+          <t>https://www.indeed.com/viewjob?jk=eb2b91e43799078b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c6c1522b73f43</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4fe4f9da167926</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=7fdf2977d8bc9710</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Cloud Storage, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=46d445a33b21a896</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Service Consultant, Automation Enablement Security Engineer Expert</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, NoSQL, ELT, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff94dfe3f61f8ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Service Consultant, Automation Enablement Security Engineer Expert</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, NoSQL, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60c34cb21ad1a04</t>
+          <t>https://www.indeed.com/viewjob?jk=ff94dfe3f61f8ecd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac3016e7e21ad71</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee7c1d439d2be4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdab2a9da3b1d40a</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, dbt, CI/CD, Jenkins, CodeBuild, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360b105c51b4b18d</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Architect: Risk, Marketing and Admin Systems</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ecb9f752d7e5c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,42 +2026,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Engineer, Design Innovation</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93163132c02c54e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,94 +2106,94 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Data Architect and Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Numerica Credit Union</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Test Automation Engineer with Payments-6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e317823b6bba5c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Test Automation Engineer with Payments-6</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e317823b6bba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Senior Data Engineer - Labor Management</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Labor Management</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,94 +2596,94 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Architect - Python</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Velosys</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=c23106e5c23ff68d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
+          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Associate, Data Engineering</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de2bf62e20c061</t>
+          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6697755b0713d9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3cb04e6738d9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d12857fefc5ca8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783e17a455f64671</t>
+          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfd260d745b1bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96aa16f84c8967a</t>
+          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc814adf2cdb3703</t>
+          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55b20019947651</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46eaedd7e80727d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea65d8868acba12</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b807619e45bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9c91959eafed53</t>
+          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b2bce2c9812940</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1e64518676fcac</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4393b985d2091210</t>
+          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5d816788d42ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09eb55d5c694197</t>
+          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631840140778c660</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ee97e5f002d4</t>
+          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaaf90a86de8eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe3c438d66d7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac8b7fa4a60c853</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0ff4431a3d1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c53a4c9216e0995</t>
+          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcfd986b1ebbe2a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584f79c7f2b01348</t>
+          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0305cc19643f428</t>
+          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb50b37bbb6f5cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2432621208aa332e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d870d6d5195df52</t>
+          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6a5818834898d</t>
+          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2846128e67de823</t>
+          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87916fa1f771e67e</t>
+          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81477799a9456664</t>
+          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5992b4722580c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4150f2b94976f855</t>
+          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcadc314310ac96c</t>
+          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7693ddf4365b5c14</t>
+          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94868ef0548a0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fdbbee67370fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cab344a26045e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e42a60f169e1ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce62334528abae7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bb4e3917249201</t>
+          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=835ab226fc2be0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d706a31f41da183c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90b441a665b697a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becbafc58a80cab7</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5860430964f8245</t>
+          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a733eecb81cf439</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1a9285cbef027f</t>
+          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc89b76198ab3891</t>
+          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf136aa9e069500</t>
+          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d16a55a13e2024</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5931f82f1594e136</t>
+          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5580988f550d45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Sr Database Engineer (DBE)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3c0822f1dea66</t>
+          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,67 +5081,67 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700343f94239c4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a31b1d4cb43adaa5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr Database Engineer (DBE)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,59 +5151,59 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd7e06c5d782973</t>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Power BI Developer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c37835f550ddf38</t>
+          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Software Engineering Intern - DRC Team</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>StockX</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb48de65765dd65b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b144a0f72c9e40</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Admin-7</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23e88beb9094727</t>
+          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Security Compliance Specialist</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Kafka, Data Modeling, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f276a316b4b1e560</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineering Intern - DRC Team</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>StockX</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, DynamoDB, Splunk</t>
+          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b144a0f72c9e40</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Snowflake Admin-7</t>
+          <t>Data Ops Engineer-6</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a17d97b1317addaf</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Security Compliance Specialist</t>
+          <t>Python / Linux-6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f276a316b4b1e560</t>
+          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Senior Engineer, Store Efficiency</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Fact Tables, ETL, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3fde3ef9f67a33</t>
+          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Ops Engineer-6</t>
+          <t>IT Data Solutions Developer Senior</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HARBIN CLINIC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,67 +5466,67 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd603f19d5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Python / Linux-6</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d649efeb0eab93e6</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Engineer, Store Efficiency</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Foot Locker</t>
+          <t>Revelyst</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a63f900fc43c207</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer Senior</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HARBIN CLINIC</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,94 +5571,94 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281770c5a69e8a32</t>
+          <t>https://www.indeed.com/viewjob?jk=53ba3cad7c42a3af</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Analytics Migration Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9e1ad94a35fefc</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer in Merrimack, NH</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, ETL, ELT, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f0f1ff47e67993</t>
+          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Analytics Migration Engineer</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Placer.ai</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, ETL, Airflow, Git</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c5a900c2b1c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Woodcliff Lake, NJ, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Software Developer I</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Placer.ai</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Jenkins, Git, GitFlow</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+          <t>https://www.indeed.com/viewjob?jk=89ef6144b41540db</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Hayden AI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Woodcliff Lake, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911bb6b38a29babb</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ca54fa35f4880f</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Snowflake Architect-6</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Minnesota City, MN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Power BI, Tableau, MLflow, Git</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e9660980ec8a8c</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Azure Databricks Architect-6</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Revelyst</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd84103264f7db0</t>
+          <t>https://www.indeed.com/viewjob?jk=45a02b9b0db8bbb2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Adobe Cloud Architect-6</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,17 +5876,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, HDFS, Hive, HBase, YARN, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a73519f4deb64d</t>
+          <t>https://www.indeed.com/viewjob?jk=57de77eeafd2c392</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Minnesota City, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e9660980ec8a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=6186e5dd2c86d2eb</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-6</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45a02b9b0db8bbb2</t>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Adobe Cloud Architect-6</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57de77eeafd2c392</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Snowflake Architect-6</t>
+          <t>Senior Technical Data Analyst</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GHX</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, ECS, RDS, Scala, Polars, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6186e5dd2c86d2eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6b94c4bc25bde3f7</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Databricks Data Engineer(Azure + Python)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Dataflow, Cloud Storage, Scala, Snowflake, Star Schema, Terraform</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>OIPA Engineer-6</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Technical Data Analyst</t>
+          <t>Senior Compliance Automation Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>GHX</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Scala, Polars, Snowflake, Power BI, Tableau, Git</t>
+          <t>RDS, Dataflow, Scala, Data Modeling, Dimensional Modeling, Power BI, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,19 +6131,19 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b94c4bc25bde3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3083d09f76d381ed</t>
+          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OIPA Engineer-6</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3f58aa04eb2d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0af3bdc55914e6</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Compliance Automation Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,17 +6226,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Data Modeling, Dimensional Modeling, Power BI, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Analyst_EDM-7</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, MLOps, CI/CD, Jenkins, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
+          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>Teradata Developer-6</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Scala, Oracle, ETL, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Senior Java Developer (AWS)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b656f77d8ee725</t>
+          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise Architect - Data</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mid-Hudson Valley Federal Credit Union</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Kingston, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ELT, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b11459048a088be</t>
+          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Business Analytics Product Owner</t>
+          <t>IAM DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,190 +6436,15 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Git, Python, SQL</t>
+          <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce00115bdc991072</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Data Analyst_EDM-7</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Data Modeling, Star Schema, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=327d2a62ab181652</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Teradata Developer-6</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f4b8e609b40433</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Senior Java Developer (AWS)</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61573c8f16db4391</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Enterprise Architect - Data</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0492824849a588e</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>IAM DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff2f3126ab0313df</t>
         </is>

--- a/results/job_matches_2026-03-12.xlsx
+++ b/results/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,72 +526,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
+          <t>https://www.indeed.com/viewjob?jk=176be754bb6a10a9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IT Compliance Consultant</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
+          <t>https://www.indeed.com/viewjob?jk=8c85f868b397f933</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Intern</t>
+          <t>IT Compliance Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Green Gas USA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, MapReduce, HBase, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b261dd4077731</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer - AI/ML</t>
+          <t>Data Engineer - Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Green Gas USA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
+          <t>https://www.indeed.com/viewjob?jk=5a49e9369fa229a4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-6</t>
+          <t>AI Engineer - AI/ML</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=01e1e9aee623c595</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Qlik Data Engineer-6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shopko Optical</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
+          <t>https://www.indeed.com/viewjob?jk=a44311f290c68fcb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior .Net Developer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27509362b1441a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f42170db9ad527f6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior .Net Developer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3769548913d0b45</t>
+          <t>https://www.indeed.com/viewjob?jk=879e206372c893dd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Shopko Optical</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, Azure, GCP, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5b4ffc7f2a589f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Senior .Net Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
+          <t>https://www.indeed.com/viewjob?jk=a27509362b1441a6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer-6</t>
+          <t>Senior .Net Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f3769548913d0b45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II- Onsite (77092)</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sagis, PLLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
+          <t>https://www.indeed.com/viewjob?jk=cd54000b5e0224f2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b83b776a063f69</t>
+          <t>https://www.indeed.com/viewjob?jk=2517e65f484b1492</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c86878a4a53e1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8cee90a5b725d3ee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II- Onsite (77092)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Sagis, PLLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Splunk</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5519eeb85983ba64</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0edc7f1332750</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>JET Infrastructure Holding IA LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, PostgreSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Product Engineer – Java Spring Boot - Full Stack</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-6</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Senior Databricks Developer-6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f87b2affa9c6fa4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Service Consultant, Automation Enablement Security Engineer Expert</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, NoSQL, ELT, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff94dfe3f61f8ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=97cce3f409dc593c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Architect: Risk, Marketing and Admin Systems</t>
+          <t>Service Consultant, Automation Enablement Security Engineer Expert</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,69 +1711,69 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, NoSQL, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ff94dfe3f61f8ecd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>Architect: Risk, Marketing and Admin Systems</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=3af1079eba06f3e4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, NoSQL, ETL, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
+          <t>https://www.indeed.com/viewjob?jk=85b88823e484c1da</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,69 +1851,69 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ecb9f752d7e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=234fd2801a1e56d5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PythonPySpark Engineer-6</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ecb9f752d7e5c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Enterprise Info Mgmt Platform Admin</t>
+          <t>PythonPySpark Engineer-6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Azure, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7bc848d1912566</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Managing Data Architect - Azure Databricks Architect</t>
+          <t>Senior Enterprise Info Mgmt Platform Admin</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
+          <t>https://www.indeed.com/viewjob?jk=128cc03b9e23fea5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scientific Software Engineer</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Solid Power</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Scientific Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Research Foundation CUNY</t>
+          <t>Solid Power</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,69 +2026,69 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
+          <t>https://www.indeed.com/viewjob?jk=401153734bd96b6d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Grid Dynamics</t>
+          <t>Research Foundation CUNY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Annandale, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3a83e2c695668c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer II - Scala</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Grid Dynamics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Annandale, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
+          <t>https://www.indeed.com/viewjob?jk=d832009392223d37</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Databricks Engineer</t>
+          <t>Software Engineer II - Scala</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, Databricks, Spark, Scala, DynamoDB, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f27f10d00e06f337</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect and Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Numerica Credit Union</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior SOX Automation Engineer</t>
+          <t>Data Architect and Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Numerica Credit Union</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd757a00dd02d2f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Test Automation Engineer with Payments-6</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e317823b6bba5c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-6</t>
+          <t>Senior SOX Automation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f705e2f549ccf63</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Test Automation Engineer with Payments-6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e317823b6bba5c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Sr DevOPS Engineer-6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4397b190052ca4</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sabio Infotech</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Quality Engineer - BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Sabio Infotech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,129 +2596,129 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+          <t>https://www.indeed.com/viewjob?jk=ecc14345bea80d80</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Architect - Python</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Velosys</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c23106e5c23ff68d</t>
+          <t>https://www.indeed.com/viewjob?jk=c89c64503f57120f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Sr. Engineer - Data Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Cassandra, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28d4f20bd8062e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b07814ed4c1025b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1578ead101425079</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc9f9684c6f3b43</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1336c3579934080a</t>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Engineering</t>
+          <t>Architect - Python</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Velosys</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445bf5e93a44c3ef</t>
+          <t>https://www.indee